--- a/backend/app/resources/templates/mes/route_step.xlsx
+++ b/backend/app/resources/templates/mes/route_step.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:S1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -437,6 +437,9 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -516,6 +519,21 @@
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>convert_to</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>convert_mode</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>convert_ratio</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -532,14 +550,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -695,7 +713,6 @@
           <t>route code (CODE or CODE@version)</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -713,7 +730,6 @@
           <t>TRUE / FALSE</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -758,7 +774,6 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -776,7 +791,6 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Blank: unlimited</t>
@@ -799,7 +813,6 @@
           <t>same_step / next_step</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -817,7 +830,6 @@
           <t>TRUE / FALSE</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -835,7 +847,6 @@
           <t>TRUE / FALSE</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -853,7 +864,6 @@
           <t>TRUE / FALSE</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -871,43 +881,112 @@
           <t>TRUE / FALSE</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>convert_to</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Convert units to</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>text (max 200)</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-    </row>
-    <row r="18"/>
+          <t>die / strip / package / unit</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Converts the lot's units automatically at track out</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>convert_mode</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Conversion mode</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>map / split / assemble</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>when convert_to = any</t>
+        </is>
+      </c>
+    </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Rows are matched by route, seq: existing rows are updated, others created.</t>
+          <t>convert_ratio</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Conversion ratio</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>when convert_mode = split / assemble</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Split: outputs per unit; assemble: units per output</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>text (max 200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Rows are matched by route, seq: existing rows are updated, others created.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Only the first sheet is imported; all rows succeed or nothing is saved (max 5000).</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Leave unused columns blank or delete them; add attr:&lt;code&gt; columns for custom attributes.</t>
         </is>
